--- a/tools/importer/reports/import-about-page.report.xlsx
+++ b/tools/importer/reports/import-about-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>about-page</t>
   </si>
   <si>
-    <t>2026-06-24T10:52:09.803Z</t>
+    <t>2026-06-24T15:22:38.457Z</t>
   </si>
   <si>
     <t>About Deluxe: The Payments and Data Solutions Company</t>
